--- a/data/nzd0083/nzd0083.xlsx
+++ b/data/nzd0083/nzd0083.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G347"/>
+  <dimension ref="A1:G348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9807,6 +9807,33 @@
       <c r="G347" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>329.19</v>
+      </c>
+      <c r="C348" t="n">
+        <v>318.94</v>
+      </c>
+      <c r="D348" t="n">
+        <v>333.75</v>
+      </c>
+      <c r="E348" t="n">
+        <v>338.51</v>
+      </c>
+      <c r="F348" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B359"/>
+  <dimension ref="A1:B360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13414,6 +13441,16 @@
       </c>
       <c r="B359" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -13582,28 +13619,28 @@
         <v>0.1314</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2622050203943915</v>
+        <v>0.2572545781783247</v>
       </c>
       <c r="J2" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K2" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09919046596536385</v>
+        <v>0.09591634793383486</v>
       </c>
       <c r="M2" t="n">
-        <v>4.495560642966616</v>
+        <v>4.504437598999116</v>
       </c>
       <c r="N2" t="n">
-        <v>33.03162390600433</v>
+        <v>33.12867415115385</v>
       </c>
       <c r="O2" t="n">
-        <v>5.747314495136344</v>
+        <v>5.755751397615592</v>
       </c>
       <c r="P2" t="n">
-        <v>330.3802078973151</v>
+        <v>330.4340266613486</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13660,28 +13697,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1669816646654921</v>
+        <v>0.1601944729709577</v>
       </c>
       <c r="J3" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K3" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04059319006554951</v>
+        <v>0.03735205819697707</v>
       </c>
       <c r="M3" t="n">
-        <v>4.740765649184968</v>
+        <v>4.754841891667646</v>
       </c>
       <c r="N3" t="n">
-        <v>34.86358658437374</v>
+        <v>35.12447597811384</v>
       </c>
       <c r="O3" t="n">
-        <v>5.904539489610832</v>
+        <v>5.926590586341682</v>
       </c>
       <c r="P3" t="n">
-        <v>325.7226303731815</v>
+        <v>325.7964173708507</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13738,28 +13775,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07120437726635512</v>
+        <v>0.0660154892384078</v>
       </c>
       <c r="J4" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K4" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01436898228376593</v>
+        <v>0.01231872596583206</v>
       </c>
       <c r="M4" t="n">
-        <v>3.544856415291918</v>
+        <v>3.556392717165148</v>
       </c>
       <c r="N4" t="n">
-        <v>18.39867779579505</v>
+        <v>18.55686321832321</v>
       </c>
       <c r="O4" t="n">
-        <v>4.289367994914292</v>
+        <v>4.307767776740433</v>
       </c>
       <c r="P4" t="n">
-        <v>340.4507195323874</v>
+        <v>340.5071305615811</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13816,28 +13853,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05543848316088987</v>
+        <v>0.05005237549215389</v>
       </c>
       <c r="J5" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K5" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004876762323718031</v>
+        <v>0.003978353494521469</v>
       </c>
       <c r="M5" t="n">
-        <v>4.536899984084334</v>
+        <v>4.541860857648942</v>
       </c>
       <c r="N5" t="n">
-        <v>33.17820084672856</v>
+        <v>33.31015428146178</v>
       </c>
       <c r="O5" t="n">
-        <v>5.760052156597939</v>
+        <v>5.771494978033142</v>
       </c>
       <c r="P5" t="n">
-        <v>345.9553659858848</v>
+        <v>346.0139210896575</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13894,28 +13931,28 @@
         <v>0.1022</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2305041295810548</v>
+        <v>0.2218761656415851</v>
       </c>
       <c r="J6" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K6" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05506713381686701</v>
+        <v>0.05097108403397888</v>
       </c>
       <c r="M6" t="n">
-        <v>5.497503031244035</v>
+        <v>5.517499808777186</v>
       </c>
       <c r="N6" t="n">
-        <v>48.23372231224675</v>
+        <v>48.67867267499199</v>
       </c>
       <c r="O6" t="n">
-        <v>6.945050202284124</v>
+        <v>6.977010296322629</v>
       </c>
       <c r="P6" t="n">
-        <v>348.6326750056886</v>
+        <v>348.7264739705246</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13953,7 +13990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G347"/>
+  <dimension ref="A1:G348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26795,6 +26832,43 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-35.50329706780839,174.46920695294816</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-35.50401869654835,174.4693970308922</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-35.504671917640195,174.46985076786643</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-35.50534838614594,174.47026223091703</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-35.505966638682615,174.47074277724982</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0083/nzd0083.xlsx
+++ b/data/nzd0083/nzd0083.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G348"/>
+  <dimension ref="A1:G350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9832,6 +9832,60 @@
         <v>340.5</v>
       </c>
       <c r="G348" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>328.06</v>
+      </c>
+      <c r="C349" t="n">
+        <v>317.2</v>
+      </c>
+      <c r="D349" t="n">
+        <v>332.86</v>
+      </c>
+      <c r="E349" t="n">
+        <v>336.04</v>
+      </c>
+      <c r="F349" t="n">
+        <v>337.23</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>328.84</v>
+      </c>
+      <c r="C350" t="n">
+        <v>318.69</v>
+      </c>
+      <c r="D350" t="n">
+        <v>334.45</v>
+      </c>
+      <c r="E350" t="n">
+        <v>337.07</v>
+      </c>
+      <c r="F350" t="n">
+        <v>339.1</v>
+      </c>
+      <c r="G350" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9848,7 +9902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B360"/>
+  <dimension ref="A1:B362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13451,6 +13505,26 @@
       </c>
       <c r="B360" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -13619,28 +13693,28 @@
         <v>0.1314</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2572545781783247</v>
+        <v>0.2466640578998292</v>
       </c>
       <c r="J2" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K2" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09591634793383486</v>
+        <v>0.08886982847909741</v>
       </c>
       <c r="M2" t="n">
-        <v>4.504437598999116</v>
+        <v>4.524723278424043</v>
       </c>
       <c r="N2" t="n">
-        <v>33.12867415115385</v>
+        <v>33.3837646130686</v>
       </c>
       <c r="O2" t="n">
-        <v>5.755751397615592</v>
+        <v>5.777868518153437</v>
       </c>
       <c r="P2" t="n">
-        <v>330.4340266613486</v>
+        <v>330.5495059099193</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13697,28 +13771,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1601944729709577</v>
+        <v>0.1457179657371123</v>
       </c>
       <c r="J3" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K3" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03735205819697707</v>
+        <v>0.03080247062111874</v>
       </c>
       <c r="M3" t="n">
-        <v>4.754841891667646</v>
+        <v>4.787070599644071</v>
       </c>
       <c r="N3" t="n">
-        <v>35.12447597811384</v>
+        <v>35.75612323071227</v>
       </c>
       <c r="O3" t="n">
-        <v>5.926590586341682</v>
+        <v>5.979642399902545</v>
       </c>
       <c r="P3" t="n">
-        <v>325.7964173708507</v>
+        <v>325.9542683161791</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13775,28 +13849,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0660154892384078</v>
+        <v>0.05574126996137838</v>
       </c>
       <c r="J4" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K4" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01231872596583206</v>
+        <v>0.008734164450296733</v>
       </c>
       <c r="M4" t="n">
-        <v>3.556392717165148</v>
+        <v>3.58029641871952</v>
       </c>
       <c r="N4" t="n">
-        <v>18.55686321832321</v>
+        <v>18.87208879272531</v>
       </c>
       <c r="O4" t="n">
-        <v>4.307767776740433</v>
+        <v>4.344201744017572</v>
       </c>
       <c r="P4" t="n">
-        <v>340.5071305615811</v>
+        <v>340.6191585278114</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13853,28 +13927,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05005237549215389</v>
+        <v>0.03718002064182529</v>
       </c>
       <c r="J5" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K5" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003978353494521469</v>
+        <v>0.002185483284079748</v>
       </c>
       <c r="M5" t="n">
-        <v>4.541860857648942</v>
+        <v>4.559737283897146</v>
       </c>
       <c r="N5" t="n">
-        <v>33.31015428146178</v>
+        <v>33.776843492484</v>
       </c>
       <c r="O5" t="n">
-        <v>5.771494978033142</v>
+        <v>5.81178488009355</v>
       </c>
       <c r="P5" t="n">
-        <v>346.0139210896575</v>
+        <v>346.1542812659636</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13931,28 +14005,28 @@
         <v>0.1022</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2218761656415851</v>
+        <v>0.2021952922346834</v>
       </c>
       <c r="J6" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K6" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05097108403397888</v>
+        <v>0.04197423375134779</v>
       </c>
       <c r="M6" t="n">
-        <v>5.517499808777186</v>
+        <v>5.570268618495158</v>
       </c>
       <c r="N6" t="n">
-        <v>48.67867267499199</v>
+        <v>49.93832501915116</v>
       </c>
       <c r="O6" t="n">
-        <v>6.977010296322629</v>
+        <v>7.066705386469084</v>
       </c>
       <c r="P6" t="n">
-        <v>348.7264739705246</v>
+        <v>348.9410734318343</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13990,7 +14064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G348"/>
+  <dimension ref="A1:G350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26869,6 +26943,80 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-35.5033005167872,174.46919523132092</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-35.50402400737989,174.469378981507</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-35.50467488198904,174.46984165041135</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-35.50535866207798,174.470238073616</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-35.50598202675581,174.47071202857816</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-35.50329813607628,174.46920332235575</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-35.50401945959902,174.46939443758987</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-35.50466958612939,174.46985793889806</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-35.50535437697329,174.4702481473091</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-35.50597322684944,174.4707296126824</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0083/nzd0083.xlsx
+++ b/data/nzd0083/nzd0083.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G350"/>
+  <dimension ref="A1:G351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9886,6 +9886,33 @@
         <v>339.1</v>
       </c>
       <c r="G350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>328.46</v>
+      </c>
+      <c r="C351" t="n">
+        <v>320.36</v>
+      </c>
+      <c r="D351" t="n">
+        <v>335.78</v>
+      </c>
+      <c r="E351" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="F351" t="n">
+        <v>340.24</v>
+      </c>
+      <c r="G351" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9902,7 +9929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B362"/>
+  <dimension ref="A1:B363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13525,6 +13552,16 @@
       </c>
       <c r="B362" t="n">
         <v>0.48</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>-0.44</v>
       </c>
     </row>
   </sheetData>
@@ -13693,28 +13730,28 @@
         <v>0.1314</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2466640578998292</v>
+        <v>0.2414609180726176</v>
       </c>
       <c r="J2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08886982847909741</v>
+        <v>0.08549560666338119</v>
       </c>
       <c r="M2" t="n">
-        <v>4.524723278424043</v>
+        <v>4.5341548089541</v>
       </c>
       <c r="N2" t="n">
-        <v>33.3837646130686</v>
+        <v>33.50451443109301</v>
       </c>
       <c r="O2" t="n">
-        <v>5.777868518153437</v>
+        <v>5.788308425705477</v>
       </c>
       <c r="P2" t="n">
-        <v>330.5495059099193</v>
+        <v>330.6064617974573</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13771,28 +13808,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1457179657371123</v>
+        <v>0.1400506238869513</v>
       </c>
       <c r="J3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03080247062111874</v>
+        <v>0.02850737565744133</v>
       </c>
       <c r="M3" t="n">
-        <v>4.787070599644071</v>
+        <v>4.7972531275847</v>
       </c>
       <c r="N3" t="n">
-        <v>35.75612323071227</v>
+        <v>35.91037993064661</v>
       </c>
       <c r="O3" t="n">
-        <v>5.979642399902545</v>
+        <v>5.992527007085292</v>
       </c>
       <c r="P3" t="n">
-        <v>325.9542683161791</v>
+        <v>326.0163055659506</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13849,28 +13886,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05574126996137838</v>
+        <v>0.05196472953249752</v>
       </c>
       <c r="J4" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K4" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008734164450296733</v>
+        <v>0.007604533331055818</v>
       </c>
       <c r="M4" t="n">
-        <v>3.58029641871952</v>
+        <v>3.586622271679623</v>
       </c>
       <c r="N4" t="n">
-        <v>18.87208879272531</v>
+        <v>18.9320298972094</v>
       </c>
       <c r="O4" t="n">
-        <v>4.344201744017572</v>
+        <v>4.35109525260128</v>
       </c>
       <c r="P4" t="n">
-        <v>340.6191585278114</v>
+        <v>340.6604982225137</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13927,28 +13964,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03718002064182529</v>
+        <v>0.0318485018813166</v>
       </c>
       <c r="J5" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K5" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002185483284079748</v>
+        <v>0.001604558121050204</v>
       </c>
       <c r="M5" t="n">
-        <v>4.559737283897146</v>
+        <v>4.565700669318005</v>
       </c>
       <c r="N5" t="n">
-        <v>33.776843492484</v>
+        <v>33.9072672083582</v>
       </c>
       <c r="O5" t="n">
-        <v>5.81178488009355</v>
+        <v>5.822994694172252</v>
       </c>
       <c r="P5" t="n">
-        <v>346.1542812659636</v>
+        <v>346.2126424465227</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14005,28 +14042,28 @@
         <v>0.1022</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2021952922346834</v>
+        <v>0.193769689257352</v>
       </c>
       <c r="J6" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K6" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04197423375134779</v>
+        <v>0.03851036007370279</v>
       </c>
       <c r="M6" t="n">
-        <v>5.570268618495158</v>
+        <v>5.590295821552923</v>
       </c>
       <c r="N6" t="n">
-        <v>49.93832501915116</v>
+        <v>50.362392180428</v>
       </c>
       <c r="O6" t="n">
-        <v>7.066705386469084</v>
+        <v>7.0966465447018</v>
       </c>
       <c r="P6" t="n">
-        <v>348.9410734318343</v>
+        <v>349.0333038372343</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14064,7 +14101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G350"/>
+  <dimension ref="A1:G351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27017,6 +27054,43 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-35.503299295909876,174.4691993805696</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-35.50401436241951,174.4694117608484</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-35.504665156257715,174.46987156385694</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-35.50534967583807,174.4702591990294</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-35.505967862199405,174.47074033240173</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
